--- a/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/O2/75K/Edited/AB Polyol O2_edited.xlsx
+++ b/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/O2/75K/Edited/AB Polyol O2_edited.xlsx
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.613</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0615</v>
+        <v>-0.0622</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
